--- a/Result/profitability/6620.xlsx
+++ b/Result/profitability/6620.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM31"/>
+  <dimension ref="A1:AM32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3868,10 +3868,10 @@
         <v>322</v>
       </c>
       <c r="L28" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9375</v>
+        <v>0.92625</v>
       </c>
       <c r="N28" t="n">
         <v>95.73125</v>
@@ -3901,10 +3901,10 @@
         <v>114.2</v>
       </c>
       <c r="W28" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="X28" t="n">
-        <v>6.344827586206897</v>
+        <v>6.03448275862069</v>
       </c>
       <c r="Y28" t="n">
         <v>11.17</v>
@@ -3913,10 +3913,10 @@
         <v>0.1436840751222022</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.917808219178082</v>
+        <v>1.794520547945206</v>
       </c>
       <c r="AC28" t="n">
         <v>-10.96000000000001</v>
@@ -3998,7 +3998,7 @@
         <v>1.34</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9712500000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>93.05875</v>
@@ -4028,10 +4028,10 @@
         <v>114.3</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.7899999999999998</v>
+        <v>-0.7</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.3708920187793426</v>
+        <v>-0.3431372549019608</v>
       </c>
       <c r="Y29" t="n">
         <v>-10.42999999999999</v>
@@ -4125,7 +4125,7 @@
         <v>1.12</v>
       </c>
       <c r="M30" t="n">
-        <v>1.03</v>
+        <v>1.01875</v>
       </c>
       <c r="N30" t="n">
         <v>91.49875</v>
@@ -4252,7 +4252,7 @@
         <v>0.46</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9837500000000001</v>
+        <v>0.9725000000000001</v>
       </c>
       <c r="N31" t="n">
         <v>89.16625000000001</v>
@@ -4333,6 +4333,133 @@
       </c>
       <c r="AM31" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6620</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>212</v>
+      </c>
+      <c r="D32" t="n">
+        <v>43</v>
+      </c>
+      <c r="E32" t="n">
+        <v>169</v>
+      </c>
+      <c r="F32" t="n">
+        <v>79.89</v>
+      </c>
+      <c r="G32" t="n">
+        <v>49</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>23.25%</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>12</v>
+      </c>
+      <c r="J32" t="n">
+        <v>61</v>
+      </c>
+      <c r="K32" t="n">
+        <v>32</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="N32" t="n">
+        <v>86.66875</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W32" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="X32" t="n">
+        <v>-0.5869565217391304</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-1.310000000000002</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-0.01613300492610836</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>-0.9068627450980392</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>-9.019999999999996</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>-0.101450905409965</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK32" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
